--- a/data/macro/USA/FED Target Rate.xlsx
+++ b/data/macro/USA/FED Target Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A83905-94D4-4644-AFF5-002858089061}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFED5B1-6191-4323-9CF4-59F8A051146B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10155" yWindow="780" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fed Target Rate" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2177,6 +2186,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2184,7 +2194,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3077,13 +3086,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G303"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.125" style="9" customWidth="1"/>
-    <col min="5" max="7" width="9.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.09765625" style="9" customWidth="1"/>
+    <col min="5" max="7" width="9.09765625" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
@@ -9972,7 +9981,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9EAB5-0149-4548-96A8-B9F3C1083AD8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9983,12 +9992,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E03F4A-9B60-4F24-A253-F9B33163B43A}">
   <dimension ref="B2:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>

--- a/data/macro/USA/FED Target Rate.xlsx
+++ b/data/macro/USA/FED Target Rate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030A7C9E-F9CA-4200-9969-A98B848E79A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95144205-8C2F-4856-A103-5F9094F7BF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,28 +73,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -102,22 +102,17 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Verdana"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -146,29 +141,29 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="백분율" xfId="1" builtinId="5"/>
@@ -2090,6 +2085,9 @@
                   <c:v>3.7499999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="296">
+                  <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="297">
                   <c:v>3.7499999999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
@@ -3135,17 +3133,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G311"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.09765625" style="9" customWidth="1"/>
-    <col min="5" max="7" width="9.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="9" customWidth="1"/>
+    <col min="5" max="7" width="9.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -3168,7 +3166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="7">
         <v>30221</v>
       </c>
@@ -3201,7 +3199,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="7">
         <v>30225</v>
       </c>
@@ -3237,7 +3235,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="7">
         <v>30231</v>
       </c>
@@ -3258,7 +3256,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="7">
         <v>30274</v>
       </c>
@@ -3279,7 +3277,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="7">
         <v>30299</v>
       </c>
@@ -3300,7 +3298,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="7">
         <v>30406</v>
       </c>
@@ -3321,7 +3319,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="7">
         <v>30461</v>
       </c>
@@ -3342,7 +3340,7 @@
         <v>8.6199999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="7">
         <v>30491</v>
       </c>
@@ -3363,7 +3361,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="7">
         <v>30511</v>
       </c>
@@ -3384,7 +3382,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="7">
         <v>30517</v>
       </c>
@@ -3405,7 +3403,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="7">
         <v>30539</v>
       </c>
@@ -3426,7 +3424,7 @@
         <v>9.4299999999999995E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="7">
         <v>30545</v>
       </c>
@@ -3447,7 +3445,7 @@
         <v>9.5600000000000004E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="7">
         <v>30574</v>
       </c>
@@ -3468,7 +3466,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="7">
         <v>30770</v>
       </c>
@@ -3489,7 +3487,7 @@
         <v>9.3700000000000006E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="7">
         <v>30868</v>
       </c>
@@ -3510,7 +3508,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="7">
         <v>30882</v>
       </c>
@@ -3531,7 +3529,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="7">
         <v>30903</v>
       </c>
@@ -3552,7 +3550,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="7">
         <v>30945</v>
       </c>
@@ -3573,7 +3571,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="7">
         <v>30952</v>
       </c>
@@ -3594,7 +3592,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="7">
         <v>30966</v>
       </c>
@@ -3615,7 +3613,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="7">
         <v>30973</v>
       </c>
@@ -3636,7 +3634,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="7">
         <v>30994</v>
       </c>
@@ -3657,7 +3655,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="7">
         <v>31009</v>
       </c>
@@ -3678,7 +3676,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="7">
         <v>31022</v>
       </c>
@@ -3699,7 +3697,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="7">
         <v>31035</v>
       </c>
@@ -3720,7 +3718,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="7">
         <v>31040</v>
       </c>
@@ -3741,7 +3739,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="7">
         <v>31071</v>
       </c>
@@ -3762,7 +3760,7 @@
         <v>8.1199999999999994E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="7">
         <v>31092</v>
       </c>
@@ -3783,7 +3781,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="7">
         <v>31134</v>
       </c>
@@ -3804,7 +3802,7 @@
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="7">
         <v>31162</v>
       </c>
@@ -3825,7 +3823,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="7">
         <v>31187</v>
       </c>
@@ -3846,7 +3844,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="7">
         <v>31239</v>
       </c>
@@ -3867,7 +3865,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="7">
         <v>31253</v>
       </c>
@@ -3888,7 +3886,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="7">
         <v>31280</v>
       </c>
@@ -3909,7 +3907,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="7">
         <v>31296</v>
       </c>
@@ -3930,7 +3928,7 @@
         <v>7.8100000000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="7">
         <v>31399</v>
       </c>
@@ -3951,7 +3949,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="7">
         <v>31478</v>
       </c>
@@ -3972,7 +3970,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="7">
         <v>31504</v>
       </c>
@@ -3993,7 +3991,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7">
       <c r="A40" s="7">
         <v>31523</v>
       </c>
@@ -4014,7 +4012,7 @@
         <v>7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7">
       <c r="A41" s="7">
         <v>31554</v>
       </c>
@@ -4035,7 +4033,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7">
       <c r="A42" s="7">
         <v>31568</v>
       </c>
@@ -4056,7 +4054,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7">
       <c r="A43" s="7">
         <v>31604</v>
       </c>
@@ -4077,7 +4075,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7">
       <c r="A44" s="7">
         <v>31645</v>
       </c>
@@ -4098,7 +4096,7 @@
         <v>6.3700000000000007E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7">
       <c r="A45" s="7">
         <v>31782</v>
       </c>
@@ -4119,7 +4117,7 @@
         <v>5.8700000000000002E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46" s="7">
         <v>31897</v>
       </c>
@@ -4140,7 +4138,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47" s="7">
         <v>31919</v>
       </c>
@@ -4161,7 +4159,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7">
       <c r="A48" s="7">
         <v>31960</v>
       </c>
@@ -4182,7 +4180,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7">
       <c r="A49" s="7">
         <v>32016</v>
       </c>
@@ -4203,7 +4201,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7">
       <c r="A50" s="7">
         <v>32023</v>
       </c>
@@ -4224,7 +4222,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7">
       <c r="A51" s="7">
         <v>32024</v>
       </c>
@@ -4245,7 +4243,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7">
       <c r="A52" s="7">
         <v>32044</v>
       </c>
@@ -4266,7 +4264,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7">
       <c r="A53" s="7">
         <v>32085</v>
       </c>
@@ -4287,7 +4285,7 @@
         <v>7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7">
       <c r="A54" s="7">
         <v>32170</v>
       </c>
@@ -4308,7 +4306,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7">
       <c r="A55" s="7">
         <v>32184</v>
       </c>
@@ -4329,7 +4327,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7">
       <c r="A56" s="7">
         <v>32232</v>
       </c>
@@ -4350,7 +4348,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7">
       <c r="A57" s="7">
         <v>32272</v>
       </c>
@@ -4371,7 +4369,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7">
       <c r="A58" s="7">
         <v>32288</v>
       </c>
@@ -4392,7 +4390,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7">
       <c r="A59" s="7">
         <v>32316</v>
       </c>
@@ -4413,7 +4411,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7">
       <c r="A60" s="7">
         <v>32325</v>
       </c>
@@ -4434,7 +4432,7 @@
         <v>7.4300000000000005E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7">
       <c r="A61" s="7">
         <v>32343</v>
       </c>
@@ -4455,7 +4453,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7">
       <c r="A62" s="7">
         <v>32363</v>
       </c>
@@ -4476,7 +4474,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7">
       <c r="A63" s="7">
         <v>32364</v>
       </c>
@@ -4497,7 +4495,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7">
       <c r="A64" s="7">
         <v>32464</v>
       </c>
@@ -4518,7 +4516,7 @@
         <v>8.1199999999999994E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7">
       <c r="A65" s="7">
         <v>32469</v>
       </c>
@@ -4539,7 +4537,7 @@
         <v>8.3099999999999993E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7">
       <c r="A66" s="7">
         <v>32492</v>
       </c>
@@ -4560,7 +4558,7 @@
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7">
       <c r="A67" s="7">
         <v>32513</v>
       </c>
@@ -4596,7 +4594,7 @@
         <v>8.6800000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7">
       <c r="A68" s="7">
         <v>32548</v>
       </c>
@@ -4617,7 +4615,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7">
       <c r="A69" s="7">
         <v>32553</v>
       </c>
@@ -4638,7 +4636,7 @@
         <v>9.1200000000000003E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7">
       <c r="A70" s="7">
         <v>32563</v>
       </c>
@@ -4659,7 +4657,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7">
       <c r="A71" s="7">
         <v>32645</v>
       </c>
@@ -4680,7 +4678,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7">
       <c r="A72" s="7">
         <v>32665</v>
       </c>
@@ -4701,7 +4699,7 @@
         <v>9.8100000000000007E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7">
       <c r="A73" s="7">
         <v>32696</v>
       </c>
@@ -4722,7 +4720,7 @@
         <v>9.5600000000000004E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7">
       <c r="A74" s="7">
         <v>32716</v>
       </c>
@@ -4743,7 +4741,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7">
       <c r="A75" s="7">
         <v>32800</v>
       </c>
@@ -4764,7 +4762,7 @@
         <v>9.06E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7">
       <c r="A76" s="7">
         <v>32818</v>
       </c>
@@ -4785,7 +4783,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7">
       <c r="A77" s="7">
         <v>32862</v>
       </c>
@@ -4806,7 +4804,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7">
       <c r="A78" s="7">
         <v>33067</v>
       </c>
@@ -4827,7 +4825,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7">
       <c r="A79" s="7">
         <v>33175</v>
       </c>
@@ -4848,7 +4846,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7">
       <c r="A80" s="7">
         <v>33191</v>
       </c>
@@ -4869,7 +4867,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7">
       <c r="A81" s="7">
         <v>33214</v>
       </c>
@@ -4890,7 +4888,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7">
       <c r="A82" s="7">
         <v>33226</v>
       </c>
@@ -4911,7 +4909,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7">
       <c r="A83" s="7">
         <v>33247</v>
       </c>
@@ -4932,7 +4930,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7">
       <c r="A84" s="7">
         <v>33270</v>
       </c>
@@ -4953,7 +4951,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7">
       <c r="A85" s="7">
         <v>33305</v>
       </c>
@@ -4974,7 +4972,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7">
       <c r="A86" s="7">
         <v>33358</v>
       </c>
@@ -4995,7 +4993,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7">
       <c r="A87" s="7">
         <v>33456</v>
       </c>
@@ -5016,7 +5014,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7">
       <c r="A88" s="7">
         <v>33494</v>
       </c>
@@ -5037,7 +5035,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7">
       <c r="A89" s="7">
         <v>33542</v>
       </c>
@@ -5058,7 +5056,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7">
       <c r="A90" s="7">
         <v>33548</v>
       </c>
@@ -5079,7 +5077,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7">
       <c r="A91" s="7">
         <v>33578</v>
       </c>
@@ -5100,7 +5098,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7">
       <c r="A92" s="7">
         <v>33592</v>
       </c>
@@ -5121,7 +5119,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7">
       <c r="A93" s="7">
         <v>33703</v>
       </c>
@@ -5142,7 +5140,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7">
       <c r="A94" s="7">
         <v>33787</v>
       </c>
@@ -5163,7 +5161,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7">
       <c r="A95" s="7">
         <v>33851</v>
       </c>
@@ -5184,7 +5182,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7">
       <c r="A96" s="7">
         <v>34369</v>
       </c>
@@ -5205,7 +5203,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7">
       <c r="A97" s="7">
         <v>34415</v>
       </c>
@@ -5226,7 +5224,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7">
       <c r="A98" s="7">
         <v>34442</v>
       </c>
@@ -5247,7 +5245,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7">
       <c r="A99" s="7">
         <v>34471</v>
       </c>
@@ -5268,7 +5266,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7">
       <c r="A100" s="7">
         <v>34562</v>
       </c>
@@ -5289,7 +5287,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7">
       <c r="A101" s="7">
         <v>34653</v>
       </c>
@@ -5310,7 +5308,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7">
       <c r="A102" s="7">
         <v>34731</v>
       </c>
@@ -5331,7 +5329,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7">
       <c r="A103" s="7">
         <v>34886</v>
       </c>
@@ -5352,7 +5350,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7">
       <c r="A104" s="7">
         <v>35052</v>
       </c>
@@ -5373,7 +5371,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7">
       <c r="A105" s="7">
         <v>35095</v>
       </c>
@@ -5394,7 +5392,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7">
       <c r="A106" s="7">
         <v>35514</v>
       </c>
@@ -5415,7 +5413,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7">
       <c r="A107" s="7">
         <v>36067</v>
       </c>
@@ -5436,7 +5434,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7">
       <c r="A108" s="7">
         <v>36083</v>
       </c>
@@ -5457,7 +5455,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7">
       <c r="A109" s="7">
         <v>36116</v>
       </c>
@@ -5478,7 +5476,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7">
       <c r="A110" s="7">
         <v>36341</v>
       </c>
@@ -5499,7 +5497,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7">
       <c r="A111" s="7">
         <v>36396</v>
       </c>
@@ -5520,7 +5518,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7">
       <c r="A112" s="7">
         <v>36480</v>
       </c>
@@ -5541,7 +5539,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7">
       <c r="A113" s="7">
         <v>36558</v>
       </c>
@@ -5562,7 +5560,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7">
       <c r="A114" s="7">
         <v>36606</v>
       </c>
@@ -5583,7 +5581,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7">
       <c r="A115" s="7">
         <v>36662</v>
       </c>
@@ -5604,7 +5602,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7">
       <c r="A116" s="7">
         <v>36894</v>
       </c>
@@ -5625,7 +5623,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7">
       <c r="A117" s="7">
         <v>36922</v>
       </c>
@@ -5646,7 +5644,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7">
       <c r="A118" s="7">
         <v>36970</v>
       </c>
@@ -5667,7 +5665,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7">
       <c r="A119" s="7">
         <v>36999</v>
       </c>
@@ -5688,7 +5686,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7">
       <c r="A120" s="7">
         <v>37026</v>
       </c>
@@ -5709,7 +5707,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7">
       <c r="A121" s="7">
         <v>37069</v>
       </c>
@@ -5730,7 +5728,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7">
       <c r="A122" s="7">
         <v>37124</v>
       </c>
@@ -5751,7 +5749,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7">
       <c r="A123" s="7">
         <v>37151</v>
       </c>
@@ -5772,7 +5770,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7">
       <c r="A124" s="7">
         <v>37166</v>
       </c>
@@ -5793,7 +5791,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7">
       <c r="A125" s="7">
         <v>37201</v>
       </c>
@@ -5814,7 +5812,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7">
       <c r="A126" s="7">
         <v>37236</v>
       </c>
@@ -5835,7 +5833,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7">
       <c r="A127" s="7">
         <v>37566</v>
       </c>
@@ -5856,7 +5854,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7">
       <c r="A128" s="7">
         <v>37797</v>
       </c>
@@ -5877,7 +5875,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7">
       <c r="A129" s="7">
         <v>38168</v>
       </c>
@@ -5898,7 +5896,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7">
       <c r="A130" s="7">
         <v>38209</v>
       </c>
@@ -5919,7 +5917,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7">
       <c r="A131" s="7">
         <v>38251</v>
       </c>
@@ -5955,7 +5953,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7">
       <c r="A132" s="7">
         <v>38301</v>
       </c>
@@ -5976,7 +5974,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7">
       <c r="A133" s="7">
         <v>38335</v>
       </c>
@@ -5997,7 +5995,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7">
       <c r="A134" s="7">
         <v>38385</v>
       </c>
@@ -6018,7 +6016,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7">
       <c r="A135" s="7">
         <v>38433</v>
       </c>
@@ -6039,7 +6037,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7">
       <c r="A136" s="7">
         <v>38475</v>
       </c>
@@ -6060,7 +6058,7 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7">
       <c r="A137" s="7">
         <v>38533</v>
       </c>
@@ -6081,7 +6079,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7">
       <c r="A138" s="7">
         <v>38573</v>
       </c>
@@ -6102,7 +6100,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7">
       <c r="A139" s="7">
         <v>38615</v>
       </c>
@@ -6123,7 +6121,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7">
       <c r="A140" s="7">
         <v>38657</v>
       </c>
@@ -6144,7 +6142,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7">
       <c r="A141" s="7">
         <v>38699</v>
       </c>
@@ -6165,7 +6163,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7">
       <c r="A142" s="7">
         <v>38748</v>
       </c>
@@ -6186,7 +6184,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7">
       <c r="A143" s="7">
         <v>38804</v>
       </c>
@@ -6207,7 +6205,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7">
       <c r="A144" s="7">
         <v>38847</v>
       </c>
@@ -6228,7 +6226,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7">
       <c r="A145" s="7">
         <v>38897</v>
       </c>
@@ -6249,7 +6247,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7">
       <c r="A146" s="7">
         <v>39343</v>
       </c>
@@ -6270,7 +6268,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7">
       <c r="A147" s="7">
         <v>39386</v>
       </c>
@@ -6291,7 +6289,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7">
       <c r="A148" s="7">
         <v>39427</v>
       </c>
@@ -6312,7 +6310,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7">
       <c r="A149" s="7">
         <v>39469</v>
       </c>
@@ -6333,7 +6331,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7">
       <c r="A150" s="7">
         <v>39477</v>
       </c>
@@ -6354,7 +6352,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7">
       <c r="A151" s="7">
         <v>39525</v>
       </c>
@@ -6378,7 +6376,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7">
       <c r="A152" s="7">
         <v>39568</v>
       </c>
@@ -6402,7 +6400,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7">
       <c r="A153" s="7">
         <v>39624</v>
       </c>
@@ -6426,7 +6424,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7">
       <c r="A154" s="7">
         <v>39665</v>
       </c>
@@ -6447,7 +6445,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7">
       <c r="A155" s="7">
         <v>39707</v>
       </c>
@@ -6471,7 +6469,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7">
       <c r="A156" s="7">
         <v>39729</v>
       </c>
@@ -6492,7 +6490,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7">
       <c r="A157" s="7">
         <v>39750</v>
       </c>
@@ -6516,7 +6514,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7">
       <c r="A158" s="7">
         <v>39798</v>
       </c>
@@ -6540,7 +6538,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7">
       <c r="A159" s="7">
         <v>39841</v>
       </c>
@@ -6564,7 +6562,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7">
       <c r="A160" s="7">
         <v>39890</v>
       </c>
@@ -6588,7 +6586,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7">
       <c r="A161" s="7">
         <v>39932</v>
       </c>
@@ -6612,7 +6610,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7">
       <c r="A162" s="7">
         <v>39988</v>
       </c>
@@ -6636,7 +6634,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7">
       <c r="A163" s="7">
         <v>40037</v>
       </c>
@@ -6660,7 +6658,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7">
       <c r="A164" s="7">
         <v>40079</v>
       </c>
@@ -6684,7 +6682,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7">
       <c r="A165" s="7">
         <v>40121</v>
       </c>
@@ -6708,7 +6706,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7">
       <c r="A166" s="7">
         <v>40163</v>
       </c>
@@ -6732,7 +6730,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7">
       <c r="A167" s="7">
         <v>40205</v>
       </c>
@@ -6756,7 +6754,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7">
       <c r="A168" s="7">
         <v>40253</v>
       </c>
@@ -6780,7 +6778,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7">
       <c r="A169" s="7">
         <v>40296</v>
       </c>
@@ -6804,7 +6802,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7">
       <c r="A170" s="7">
         <v>40352</v>
       </c>
@@ -6828,7 +6826,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7">
       <c r="A171" s="7">
         <v>40400</v>
       </c>
@@ -6852,7 +6850,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7">
       <c r="A172" s="7">
         <v>40442</v>
       </c>
@@ -6876,7 +6874,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7">
       <c r="A173" s="7">
         <v>40485</v>
       </c>
@@ -6900,7 +6898,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7">
       <c r="A174" s="7">
         <v>40526</v>
       </c>
@@ -6924,7 +6922,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7">
       <c r="A175" s="7">
         <v>40569</v>
       </c>
@@ -6948,7 +6946,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7">
       <c r="A176" s="7">
         <v>40617</v>
       </c>
@@ -6972,7 +6970,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7">
       <c r="A177" s="7">
         <v>40660</v>
       </c>
@@ -6996,7 +6994,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7">
       <c r="A178" s="7">
         <v>40716</v>
       </c>
@@ -7020,7 +7018,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7">
       <c r="A179" s="7">
         <v>40764</v>
       </c>
@@ -7044,7 +7042,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7">
       <c r="A180" s="7">
         <v>40807</v>
       </c>
@@ -7068,7 +7066,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7">
       <c r="A181" s="7">
         <v>40849</v>
       </c>
@@ -7092,7 +7090,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7">
       <c r="A182" s="7">
         <v>40890</v>
       </c>
@@ -7116,7 +7114,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7">
       <c r="A183" s="7">
         <v>40933</v>
       </c>
@@ -7140,7 +7138,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7">
       <c r="A184" s="7">
         <v>40981</v>
       </c>
@@ -7164,7 +7162,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7">
       <c r="A185" s="7">
         <v>41024</v>
       </c>
@@ -7188,7 +7186,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7">
       <c r="A186" s="7">
         <v>41080</v>
       </c>
@@ -7212,7 +7210,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7">
       <c r="A187" s="7">
         <v>41122</v>
       </c>
@@ -7236,7 +7234,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7">
       <c r="A188" s="7">
         <v>41165</v>
       </c>
@@ -7260,7 +7258,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7">
       <c r="A189" s="7">
         <v>41206</v>
       </c>
@@ -7284,7 +7282,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7">
       <c r="A190" s="7">
         <v>41255</v>
       </c>
@@ -7308,7 +7306,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7">
       <c r="A191" s="7">
         <v>41304</v>
       </c>
@@ -7332,7 +7330,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7">
       <c r="A192" s="7">
         <v>41353</v>
       </c>
@@ -7356,7 +7354,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7">
       <c r="A193" s="7">
         <v>41395</v>
       </c>
@@ -7380,7 +7378,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7">
       <c r="A194" s="7">
         <v>41444</v>
       </c>
@@ -7404,7 +7402,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7">
       <c r="A195" s="7">
         <v>41486</v>
       </c>
@@ -7443,7 +7441,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7">
       <c r="A196" s="7">
         <v>41535</v>
       </c>
@@ -7467,7 +7465,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7">
       <c r="A197" s="7">
         <v>41577</v>
       </c>
@@ -7491,7 +7489,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7">
       <c r="A198" s="7">
         <v>41626</v>
       </c>
@@ -7515,7 +7513,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7">
       <c r="A199" s="7">
         <v>41668</v>
       </c>
@@ -7539,7 +7537,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7">
       <c r="A200" s="7">
         <v>41717</v>
       </c>
@@ -7563,7 +7561,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7">
       <c r="A201" s="7">
         <v>41759</v>
       </c>
@@ -7587,7 +7585,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7">
       <c r="A202" s="7">
         <v>41808</v>
       </c>
@@ -7611,7 +7609,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7">
       <c r="A203" s="7">
         <v>41850</v>
       </c>
@@ -7635,7 +7633,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7">
       <c r="A204" s="7">
         <v>41899</v>
       </c>
@@ -7659,7 +7657,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7">
       <c r="A205" s="7">
         <v>41941</v>
       </c>
@@ -7683,7 +7681,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7">
       <c r="A206" s="7">
         <v>41990</v>
       </c>
@@ -7707,7 +7705,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7">
       <c r="A207" s="7">
         <v>42032</v>
       </c>
@@ -7731,7 +7729,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7">
       <c r="A208" s="7">
         <v>42081</v>
       </c>
@@ -7755,7 +7753,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7">
       <c r="A209" s="7">
         <v>42123</v>
       </c>
@@ -7779,7 +7777,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7">
       <c r="A210" s="7">
         <v>42172</v>
       </c>
@@ -7803,7 +7801,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7">
       <c r="A211" s="7">
         <v>42214</v>
       </c>
@@ -7827,7 +7825,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7">
       <c r="A212" s="7">
         <v>42264</v>
       </c>
@@ -7851,7 +7849,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7">
       <c r="A213" s="7">
         <v>42305</v>
       </c>
@@ -7875,7 +7873,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7">
       <c r="A214" s="7">
         <v>42354</v>
       </c>
@@ -7899,7 +7897,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7">
       <c r="A215" s="7">
         <v>42396</v>
       </c>
@@ -7923,7 +7921,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7">
       <c r="A216" s="7">
         <v>42445</v>
       </c>
@@ -7947,7 +7945,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7">
       <c r="A217" s="7">
         <v>42487</v>
       </c>
@@ -7971,7 +7969,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7">
       <c r="A218" s="7">
         <v>42536</v>
       </c>
@@ -7995,7 +7993,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7">
       <c r="A219" s="7">
         <v>42578</v>
       </c>
@@ -8019,7 +8017,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7">
       <c r="A220" s="7">
         <v>42634</v>
       </c>
@@ -8043,7 +8041,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7">
       <c r="A221" s="7">
         <v>42676</v>
       </c>
@@ -8067,7 +8065,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7">
       <c r="A222" s="7">
         <v>42718</v>
       </c>
@@ -8091,7 +8089,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7">
       <c r="A223" s="7">
         <v>42767</v>
       </c>
@@ -8115,7 +8113,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7">
       <c r="A224" s="7">
         <v>42809</v>
       </c>
@@ -8139,7 +8137,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7">
       <c r="A225" s="7">
         <v>42858</v>
       </c>
@@ -8163,7 +8161,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7">
       <c r="A226" s="7">
         <v>42900</v>
       </c>
@@ -8187,7 +8185,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7">
       <c r="A227" s="7">
         <v>42942</v>
       </c>
@@ -8211,7 +8209,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7">
       <c r="A228" s="7">
         <v>42998</v>
       </c>
@@ -8235,7 +8233,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7">
       <c r="A229" s="7">
         <v>43040</v>
       </c>
@@ -8259,7 +8257,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7">
       <c r="A230" s="7">
         <v>43082</v>
       </c>
@@ -8283,7 +8281,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7">
       <c r="A231" s="7">
         <v>43131</v>
       </c>
@@ -8307,7 +8305,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7">
       <c r="A232" s="7">
         <v>43180</v>
       </c>
@@ -8331,7 +8329,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7">
       <c r="A233" s="7">
         <v>43222</v>
       </c>
@@ -8355,7 +8353,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7">
       <c r="A234" s="7">
         <v>43264</v>
       </c>
@@ -8379,7 +8377,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7">
       <c r="A235" s="7">
         <v>43313</v>
       </c>
@@ -8403,7 +8401,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7">
       <c r="A236" s="7">
         <v>43369</v>
       </c>
@@ -8427,7 +8425,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7">
       <c r="A237" s="7">
         <v>43412</v>
       </c>
@@ -8451,7 +8449,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7">
       <c r="A238" s="7">
         <v>43453</v>
       </c>
@@ -8475,7 +8473,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7">
       <c r="A239" s="7">
         <v>43495</v>
       </c>
@@ -8499,7 +8497,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7">
       <c r="A240" s="7">
         <v>43544</v>
       </c>
@@ -8523,7 +8521,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7">
       <c r="A241" s="7">
         <v>43586</v>
       </c>
@@ -8547,7 +8545,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7">
       <c r="A242" s="7">
         <v>43635</v>
       </c>
@@ -8571,7 +8569,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7">
       <c r="A243" s="7">
         <v>43677</v>
       </c>
@@ -8595,7 +8593,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7">
       <c r="A244" s="7">
         <v>43726</v>
       </c>
@@ -8619,7 +8617,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7">
       <c r="A245" s="7">
         <v>43768</v>
       </c>
@@ -8643,7 +8641,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7">
       <c r="A246" s="7">
         <v>43810</v>
       </c>
@@ -8667,7 +8665,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7">
       <c r="A247" s="7">
         <v>43859</v>
       </c>
@@ -8691,7 +8689,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7">
       <c r="A248" s="7">
         <v>43893</v>
       </c>
@@ -8712,7 +8710,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7">
       <c r="A249" s="7">
         <v>43905</v>
       </c>
@@ -8733,7 +8731,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7">
       <c r="A250" s="7">
         <v>43950</v>
       </c>
@@ -8757,7 +8755,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7">
       <c r="A251" s="7">
         <v>43992</v>
       </c>
@@ -8781,7 +8779,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7">
       <c r="A252" s="7">
         <v>44041</v>
       </c>
@@ -8805,7 +8803,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7">
       <c r="A253" s="7">
         <v>44090</v>
       </c>
@@ -8829,7 +8827,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7">
       <c r="A254" s="7">
         <v>44140</v>
       </c>
@@ -8853,7 +8851,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7">
       <c r="A255" s="7">
         <v>44181</v>
       </c>
@@ -8877,7 +8875,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7">
       <c r="A256" s="7">
         <v>44223</v>
       </c>
@@ -8901,7 +8899,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7">
       <c r="A257" s="7">
         <v>44272</v>
       </c>
@@ -8925,7 +8923,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7">
       <c r="A258" s="7">
         <v>44314</v>
       </c>
@@ -8949,7 +8947,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7">
       <c r="A259" s="7">
         <v>44363</v>
       </c>
@@ -8988,7 +8986,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7">
       <c r="A260" s="7">
         <v>44405</v>
       </c>
@@ -9012,7 +9010,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7">
       <c r="A261" s="7">
         <v>44461</v>
       </c>
@@ -9036,7 +9034,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7">
       <c r="A262" s="7">
         <v>44503</v>
       </c>
@@ -9060,7 +9058,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7">
       <c r="A263" s="7">
         <v>44545</v>
       </c>
@@ -9084,7 +9082,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7">
       <c r="A264" s="7">
         <v>44587</v>
       </c>
@@ -9108,7 +9106,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7">
       <c r="A265" s="7">
         <v>44636</v>
       </c>
@@ -9132,7 +9130,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7">
       <c r="A266" s="7">
         <v>44685</v>
       </c>
@@ -9156,7 +9154,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7">
       <c r="A267" s="7">
         <v>44727</v>
       </c>
@@ -9180,7 +9178,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7">
       <c r="A268" s="7">
         <v>44769</v>
       </c>
@@ -9204,7 +9202,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7">
       <c r="A269" s="7">
         <v>44825</v>
       </c>
@@ -9228,7 +9226,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7">
       <c r="A270" s="7">
         <v>44867</v>
       </c>
@@ -9252,7 +9250,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7">
       <c r="A271" s="7">
         <v>44909</v>
       </c>
@@ -9276,7 +9274,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7">
       <c r="A272" s="7">
         <v>44958</v>
       </c>
@@ -9300,7 +9298,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7">
       <c r="A273" s="7">
         <v>45007</v>
       </c>
@@ -9324,7 +9322,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7">
       <c r="A274" s="7">
         <v>45049</v>
       </c>
@@ -9348,7 +9346,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7">
       <c r="A275" s="7">
         <v>45091</v>
       </c>
@@ -9372,7 +9370,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7">
       <c r="A276" s="7">
         <v>45133</v>
       </c>
@@ -9396,7 +9394,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7">
       <c r="A277" s="7">
         <v>45189</v>
       </c>
@@ -9420,7 +9418,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7">
       <c r="A278" s="7">
         <v>45231</v>
       </c>
@@ -9444,7 +9442,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7">
       <c r="A279" s="7">
         <v>45273</v>
       </c>
@@ -9468,7 +9466,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7">
       <c r="A280" s="7">
         <v>45322</v>
       </c>
@@ -9492,7 +9490,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7">
       <c r="A281" s="7">
         <v>45371</v>
       </c>
@@ -9516,7 +9514,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7">
       <c r="A282" s="7">
         <v>45413</v>
       </c>
@@ -9540,7 +9538,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7">
       <c r="A283" s="7">
         <v>45455</v>
       </c>
@@ -9564,7 +9562,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7">
       <c r="A284" s="7">
         <v>45504</v>
       </c>
@@ -9588,7 +9586,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7">
       <c r="A285" s="7">
         <v>45553</v>
       </c>
@@ -9612,7 +9610,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7">
       <c r="A286" s="7">
         <v>45603</v>
       </c>
@@ -9636,7 +9634,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7">
       <c r="A287" s="7">
         <v>45644</v>
       </c>
@@ -9660,7 +9658,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7">
       <c r="A288" s="7">
         <v>45686</v>
       </c>
@@ -9684,7 +9682,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7">
       <c r="A289" s="7">
         <v>45735</v>
       </c>
@@ -9708,7 +9706,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7">
       <c r="A290" s="7">
         <v>45784</v>
       </c>
@@ -9732,7 +9730,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7">
       <c r="A291" s="7">
         <v>45826</v>
       </c>
@@ -9756,7 +9754,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7">
       <c r="A292" s="7">
         <v>45868</v>
       </c>
@@ -9780,7 +9778,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7">
       <c r="A293" s="7">
         <v>45917</v>
       </c>
@@ -9804,7 +9802,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7">
       <c r="A294" s="7">
         <v>45959</v>
       </c>
@@ -9828,7 +9826,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7">
       <c r="A295" s="7">
         <v>46001</v>
       </c>
@@ -9852,7 +9850,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7">
       <c r="A296" s="7">
         <v>46050</v>
       </c>
@@ -9891,7 +9889,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7">
       <c r="A297" s="7">
         <v>46099</v>
       </c>
@@ -9915,7 +9913,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7">
       <c r="A298" s="7">
         <v>46141</v>
       </c>
@@ -9939,7 +9937,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7">
       <c r="A299" s="7">
         <v>46190</v>
       </c>
@@ -9968,11 +9966,17 @@
 )</f>
         <v>UTC-4</v>
       </c>
+      <c r="E299" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F299" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
       <c r="G299" s="10">
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:7">
       <c r="A300" s="7">
         <v>46232</v>
       </c>
@@ -9986,8 +9990,11 @@
         <f t="shared" si="6"/>
         <v>UTC-4</v>
       </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G300" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
       <c r="A301" s="7">
         <v>46281</v>
       </c>
@@ -10002,7 +10009,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7">
       <c r="A302" s="7">
         <v>46323</v>
       </c>
@@ -10017,7 +10024,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:7">
       <c r="A303" s="7">
         <v>46365</v>
       </c>
@@ -10032,7 +10039,7 @@
         <v>UTC-5</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7">
       <c r="A304" s="7">
         <v>46414</v>
       </c>
@@ -10047,7 +10054,7 @@
         <v>UTC-5</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:4">
       <c r="A305" s="7">
         <v>46463</v>
       </c>
@@ -10077,7 +10084,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:4">
       <c r="A306" s="7">
         <v>46140</v>
       </c>
@@ -10092,7 +10099,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:4">
       <c r="A307" s="7">
         <v>46547</v>
       </c>
@@ -10107,7 +10114,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:4">
       <c r="A308" s="7">
         <v>46596</v>
       </c>
@@ -10122,7 +10129,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:4">
       <c r="A309" s="7">
         <v>46645</v>
       </c>
@@ -10137,7 +10144,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:4">
       <c r="A310" s="7">
         <v>46687</v>
       </c>
@@ -10152,7 +10159,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:4">
       <c r="A311" s="7">
         <v>46729</v>
       </c>
@@ -10177,7 +10184,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9EAB5-0149-4548-96A8-B9F3C1083AD8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10188,12 +10195,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E03F4A-9B60-4F24-A253-F9B33163B43A}">
   <dimension ref="B2:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
